--- a/media/Levels/kakeraMapLevel8.xlsx
+++ b/media/Levels/kakeraMapLevel8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\81806\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\DocterRimoto\DoctorRemote_a\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5376DEFE-A858-45C1-918D-36830ABC10B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B22BA5-90CE-4399-835E-0FBE6345080C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
+    <workbookView xWindow="2508" yWindow="0" windowWidth="15660" windowHeight="12168" xr2:uid="{BDE0F5B9-DF54-47AF-B1A2-D8190B03E7B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Level_2" sheetId="1" r:id="rId1"/>
@@ -39680,28 +39680,28 @@
         <v>0</v>
       </c>
       <c r="BU86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC86">
         <v>0</v>
@@ -40132,28 +40132,28 @@
         <v>0</v>
       </c>
       <c r="BU87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC87">
         <v>0</v>
@@ -40584,28 +40584,28 @@
         <v>0</v>
       </c>
       <c r="BU88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC88">
         <v>0</v>
@@ -41036,28 +41036,28 @@
         <v>0</v>
       </c>
       <c r="BU89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC89">
         <v>0</v>
@@ -41488,28 +41488,28 @@
         <v>0</v>
       </c>
       <c r="BU90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC90">
         <v>0</v>
@@ -41940,28 +41940,28 @@
         <v>0</v>
       </c>
       <c r="BU91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC91">
         <v>0</v>
@@ -42392,28 +42392,28 @@
         <v>0</v>
       </c>
       <c r="BU92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC92" s="5">
         <v>1</v>
@@ -42844,28 +42844,28 @@
         <v>0</v>
       </c>
       <c r="BU93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BV93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC93" s="5">
         <v>1</v>
@@ -43305,19 +43305,19 @@
         <v>1</v>
       </c>
       <c r="BX94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BY94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC94" s="5">
         <v>1</v>
